--- a/FINAL_PRINT_READY/POST_SUBMISSION_EMAIL/Technical_and_Functional_Compliance_Matrix_Bank_Asia_LMS.xlsx
+++ b/FINAL_PRINT_READY/POST_SUBMISSION_EMAIL/Technical_and_Functional_Compliance_Matrix_Bank_Asia_LMS.xlsx
@@ -58,12 +58,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t/>
+          <t>Skoder LMS Enterprise is engineered on a modern N-tier, modular microservices-ready architecture using high-performance PHP/Laravel framework and PostgreSQL/Oracle enterprise database. Comprehensive system documentation, API gateway specs, HA/DR failover topology, and data flow diagrams are included in the Technical Proposal.</t>
         </is>
       </c>
     </row>
@@ -80,7 +80,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied - Fully complied. Sized for Bank Asia's on-premises enterprise DC &amp; DR deployment utilizing Dell PowerEdge R760 Rack Servers, VMware vSphere 8, and RHEL 9. Detailed server BoQ and architecture attached in Table 16 and separate Hardware Quotation.</t>
         </is>
       </c>
     </row>
@@ -104,12 +104,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Skoder Technologies operates a dedicated Level 1/2/3 technical helpdesk from 09:00 AM to 08:00 PM Sunday through Thursday, with 24/7/365 emergency on-call and remote incident resolution via ticketing portal, email, and phone.</t>
         </is>
       </c>
     </row>
@@ -126,12 +126,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. The platform includes an advanced dynamic query builder allowing custom search filters across case types, borrower TIN/NID, court stages, outstanding balances, and hearing dates with export to Excel/PDF.</t>
         </is>
       </c>
     </row>
@@ -148,12 +148,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Includes comprehensive web-based management console, Prometheus/Grafana health metrics endpoints, APM monitoring, and secure SSL VPN administrative access.</t>
         </is>
       </c>
     </row>
@@ -170,12 +170,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. 100% browser-independent responsive web interface built on HTML5, CSS3, and modern JavaScript, fully supported on latest Google Chrome, Microsoft Edge, Mozilla Firefox, and Apple Safari without plugins.</t>
         </is>
       </c>
     </row>
@@ -192,12 +192,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Supports bilingual English and Bengali (Unicode UTF-8 / Nikosh / SolaimanLipi) for legal notices, court cause lists, case summaries, and statutory reports.</t>
         </is>
       </c>
     </row>
@@ -214,12 +214,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated test execution framework supported using simulated API payloads and automated regression test scripts for UAT verification.</t>
         </is>
       </c>
     </row>
@@ -236,12 +236,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Perpetual enterprise bank-wide license covers Primary Data Center (DC), Near DR, and Far DR active-passive deployment without additional per-core or per-seat licensing penalties.</t>
         </is>
       </c>
     </row>
@@ -258,12 +258,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic Master Parameter Setup module allows authorized administrators to configure court codes, case classifications, expense heads, branch codes, and legal acts.</t>
         </is>
       </c>
     </row>
@@ -280,12 +280,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Bank Asia PLC branding, official logo, and branch headers are dynamically rendered across application headers, printable legal notices, Jari statements, and reports.</t>
         </is>
       </c>
     </row>
@@ -302,12 +302,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive administrative console provided for schema configurations, workflow rules, audit log review, role management, and routine operational maintenance.</t>
         </is>
       </c>
     </row>
@@ -324,12 +324,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Enforces TLS 1.3 / HTTPS encryption across all web interfaces and API endpoints with strong cipher suites (HSTS, forward secrecy).</t>
         </is>
       </c>
     </row>
@@ -346,12 +346,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Modular architecture allows rapid local customization of validation rules, form fields, court stages, and screen layouts based on Bank Asia's specific legal workflows.</t>
         </is>
       </c>
     </row>
@@ -368,12 +368,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Designed to operate within Bank Asia's secure internal network zone / dedicated DMZ/VLAN with mutual TLS (mTLS) and IP whitelisting for CBS integration.</t>
         </is>
       </c>
     </row>
@@ -390,12 +390,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Supports automated End-of-Day (EOD) cron scheduling, ETL batch synchronisation, and real-time delta fetching for classified loan balances and customer details.</t>
         </is>
       </c>
     </row>
@@ -412,12 +412,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Features robust RESTful and SOAP API gateways with JSON/XML payloads, JWT token authentication, and rate limiting for bidirectional CBS/peripheral system integration.</t>
         </is>
       </c>
     </row>
@@ -434,12 +434,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Strong AES-256 column-level encryption for confidential PII and financial records at rest; TLS 1.3 encryption for all data in transit across networks.</t>
         </is>
       </c>
     </row>
@@ -463,12 +463,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Built upon open, standard architectural patterns (REST APIs, microservices, OpenAPI/Swagger 3.0 specs) ensuring seamless integration with Bank Asia CBS and other banking modules.</t>
         </is>
       </c>
     </row>
@@ -485,12 +485,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Native support for enterprise Single Sign-On (SSO) via Active Directory (LDAP / Kerberos / SAML 2.0 / OAuth2 / OpenID Connect) and open banking API integration.</t>
         </is>
       </c>
     </row>
@@ -507,12 +507,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Extensible modular schema design supports dynamic custom attributes and backwards-compatible API versioning to absorb CBS upgrades without downtime.</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Native integration with Bank Asia's internal SMS Gateway (SMPP / HTTP REST) and enterprise SMTP / Microsoft Exchange email servers for automated alert delivery.</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Notification engine handles both SMS and email queues with failure retry mechanisms and delivery audit logging.</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated background scheduler dispatches upcoming court hearing reminders, legal notice deadlines, and warrant execution alerts via SMS and email on configurable intervals.</t>
         </is>
       </c>
     </row>
@@ -595,12 +595,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Provides read-replica database support and automated daily ETL pipelines / data staging views for Bank Asia's Central Data Warehouse / MIS reporting.</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive integration toolkit including REST/JSON, SOAP/XML, automated SFTP batch file exchange, and OpenAPI/Swagger documentation.</t>
         </is>
       </c>
     </row>
@@ -646,12 +646,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Case document repository maintains immutable version control, timestamped revision history, and one-click rollback/retrieval of historical file versions.</t>
         </is>
       </c>
     </row>
@@ -668,12 +668,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated real-time notifications dispatched to assigned case handlers, desk officials, and legal supervisors whenever case status or documents are modified.</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive data migration strategy, automated Excel/CSV ETL ingest utilities, data cleansing scripts, and validation audits ensure 100% legacy litigation data migration.</t>
         </is>
       </c>
     </row>
@@ -712,12 +712,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Pre-migration gap analysis, automated staging tables with validation rules, and manual reconciliation workflows handle unmapped or missing legacy attributes.</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Flexible workflow engine allows concurrent parallel tracking of civil suits (Artha Rin), criminal proceedings (NI Act 138), auction notices, and writ petitions for the same borrower.</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Parameterized business rules engine supports configurable escalation rules, mandatory legal notice statutory wait periods (e.g. 30 days under NI Act), and approval limits.</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Multi-tier permission matrix enforces granular restrictions per user role, branch, and division for drafting, maker approval, checker authorization, viewing, and exporting reports.</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Detailed enterprise deployment architecture diagram depicting Web Server, App Server, DB Cluster, CBS Gateway, SMS/Email Server, and Active Directory enclosed in Technical Proposal.</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Proposed 100% on-premises deployment adhering to Bangladesh Bank ICT Guidelines for full data sovereignty across Bank Asia Primary DC and DR sites.</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Three distinct, isolated environments (Development/Test, UAT/Staging, and Production) will be provisioned, configured, and maintained during rollout.</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. 100% perpetual bank-wide enterprise license with unlimited users, branches, and cases without recurring subscription or license expiry locks.</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular RBAC supporting administrative, legal officer, branch maker, branch checker, panel lawyer, and executive management roles with immutable audit logging.</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Passwords hashed using industry-standard bcrypt / Argon2id algorithms with cryptographic salt, ensuring zero plain-text storage.</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Database stores one-way salted cryptographic hashes adhering to Bangladesh Bank Information Security Standards.</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Configurable password complexity policy (minimum length, uppercase, lowercase, numbers, special characters, expiration intervals, password history prevention).</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Seamless Single Sign-On (SSO) supported via Active Directory LDAP / SAML 2.0 / Kerberos integration.</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Supports assigning multiple complementary roles to a single user profile while preserving strict Maker-Checker segregation of duties.</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. System administrators can reassign user roles, transfer branch assignments, and adjust approval limits instantly with full audit logging.</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Strict Maker-Checker access matrix defined and administered through graphical administrative interface.</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Menu items, form actions (Create, Edit, Delete, Authorize), and data access scopes are dynamically restricted per assigned role.</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully integrated with Microsoft Active Directory / Azure AD via secure LDAP/LDAPS for centralized authentication and automated user provisioning.</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable audit trail captures user ID, client IP, timestamp, action type, old values, and new values for every create, update, delete, and view event.</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Database-level AES-256 transparent data encryption (TDE) for data at rest and TLS 1.3 encryption for data in transit across all endpoints.</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Supports hierarchical user group definitions (Legal Division, Special Asset Management, Branch Recovery, Panel Lawyers, Executive Management).</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Parameterized security rules enforce IP whitelisting per user/branch, allowed operating business hours, and authorized application server bindings.</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Self-service password reset workflow with secure one-time password (OTP) verification sent to registered official mobile and email.</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Configurable idle session timeout (default 15 minutes) automatically terminates inactive sessions and clears client-side tokens.</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Administrators can immediately lock, deactivate, or reactivate user accounts with mandatory reason logging and audit trail recording.</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Concurrent login prevention enforces single active session per user ID; subsequent logins invalidate existing sessions or are blocked.</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Advanced ad-hoc reporting module allows authorized users to construct parameterized queries, filter audit trails, and export datasets to Excel/PDF.</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Account automatically locks after parameterized number of consecutive failed attempts (default 5 attempts), requiring admin unlock or OTP verification.</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Active-passive high-availability configuration supported with automated database replication to Bank Asia DR site and documented BCP/DR runbook.</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Engineered for 99.9% uptime with automated health checks, seamless DR failover procedures, RPO &lt; 5 minutes, and RTO &lt; 15 minutes.</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. ACID-compliant transactional database engine with Write-Ahead Logging (WAL) ensures complete data integrity and automated crash recovery upon restart.</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fault-tolerant services with state recovery mechanisms ensure zero transaction loss and immediate resumption of operations upon system reboot.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated error tracking and anomaly detection engine alerts system administrators via email and dashboard notifications upon application exceptions.</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive enterprise RBAC model strictly enforces segregation of duties between Maker, Checker, Approver, and Viewer roles.</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Pre-built connector for Microsoft Active Directory / LDAPS provides single-source credential verification and role mapping.</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Passwords stored using salted SHA-256 / bcrypt cryptographic hashing; no plain-text passwords stored under any circumstances.</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. 100% browser-independent web client compatible with Windows, macOS, and Linux on Chrome, Edge, Firefox, and Safari; backend compatible with RHEL and PostgreSQL/Oracle.</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hardened application security layer featuring rate limiting, CSRF tokens, XSS sanitization, parameterized SQL queries, and secure session headers.</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Built and audited according to OWASP Top 10 security standards; certified against SQL Injection, XSS, CSRF, broken access control, and insecure deserialization.</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated batch execution log monitors CBS daily data ingestion, records record-level success/error counts, failure reasons, and issues alert notifications.</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Global exception handling intercepts all errors, logging detailed stack traces internally while presenting secure, user-friendly messages to the end user.</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Enforces TLS 1.3 / HTTPS encryption across all client-server interactions and inter-service communications with HSTS headers.</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Audit log search console allows authorized security officers to filter logs by user ID, action type, date range, IP address, and module.</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Built on open standards (REST, container-ready, standard SQL, POSIX OS) ensuring forward compatibility with upcoming hardware, OS, and DB upgrades.</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Skoder Technologies provides rapid vulnerability remediation and hotfix patch releases within 24–48 hours upon issuance of critical security advisories.</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Supports device fingerprinting, client certificate validation, and MAC/IP binding to restrict application access to authorized corporate terminals.</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Skoder Technologies provides comprehensive Infrastructure &amp; Application Security Hardening Guidelines covering OS, DB, Web Server, and network policies.</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Compatible with enterprise SIEM solutions (Splunk, IBM QRadar, ELK), Web Application Firewalls (WAF), and endpoint protection systems.</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. 100% of underlying frameworks, libraries, and runtime dependencies are licensed under permissive enterprise open-source licenses, fully updated and free from known CVE vulnerabilities.</t>
         </is>
       </c>
     </row>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive User Group Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive User Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Built-in Maker-Checker workflow for user account provisioning and access privilege authorization.</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Built-in Maker-Checker workflow for user account provisioning and access privilege authorization.</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -2289,12 +2289,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2311,12 +2311,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2333,12 +2333,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Configurable session timeout policy enforced server-side with automatic session termination.</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hardened password security policy with encrypted salted storage, lockout policy, and self-service reset.</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Login core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hardened password security policy with encrypted salted storage, lockout policy, and self-service reset.</t>
         </is>
       </c>
     </row>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hardened password security policy with encrypted salted storage, lockout policy, and self-service reset.</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hardened password security policy with encrypted salted storage, lockout policy, and self-service reset.</t>
         </is>
       </c>
     </row>
@@ -2487,12 +2487,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Parameter Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Department with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Designation with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Functional Designation with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Case Type with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Security Status/Details with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Auction Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Business Status/ Nature with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Borrower Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Guarantor Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Loan/investment Segment nature with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Cheque Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Facility/investment Type with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2773,12 +2773,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Case Steps with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Retail Branch with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for District with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Branch with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Expense Type with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Court Type with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Court List with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2927,12 +2927,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Lawyer List with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2949,12 +2949,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Functional Designation with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2971,12 +2971,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Disposal Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Paper List with add option with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3015,12 +3015,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Paper Vendor List with add option with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for CL Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Nature Of Warrant of Arrest and status of W/A with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Expense activities with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Supreme Court (SC) Case Category with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Supreme Court (SC) Case Type with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Supreme Court (SC) Case Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Execution Criteria /Stage of Execution Case with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Appeal Bail Type with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3213,12 +3213,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for schedule charges case against bank with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for schedule charges legal affairs (Litigation/ Documentation/Others with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3257,12 +3257,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for related authority with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for HC Division and AD with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
         </is>
       </c>
     </row>
@@ -3323,12 +3323,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
         </is>
       </c>
     </row>
@@ -3411,12 +3411,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lawyer Package Bill Setup core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3455,12 +3455,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Dashboard core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time executive dashboard featuring daily court cause lists, hearing calendars, notice statuses, and recovery metrics.</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive 1st Legal Notice/ Reminder Notice core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3741,12 +3741,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3763,12 +3763,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3829,12 +3829,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Case Merit Analysis (CMA) core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3851,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -3961,12 +3961,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -3983,12 +3983,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -4005,12 +4005,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4027,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4071,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -4093,12 +4093,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -4137,12 +4137,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4225,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -4291,12 +4291,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Auction Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -4313,12 +4313,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4423,12 +4423,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4445,12 +4445,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4533,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4555,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -4577,12 +4577,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -4621,12 +4621,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -4687,12 +4687,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Account Statement Generation core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
         </is>
       </c>
     </row>
@@ -4731,12 +4731,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Bi-directional CBS integration via secure REST API gateway for real-time account data and ledger sync.</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
         </is>
       </c>
     </row>
@@ -4797,12 +4797,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Jari Statement with Certificate core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -4819,12 +4819,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
         </is>
       </c>
     </row>
@@ -4863,12 +4863,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
         </is>
       </c>
     </row>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court Suit Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -4907,12 +4907,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -4973,12 +4973,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -4995,12 +4995,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5017,12 +5017,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -5105,12 +5105,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -5127,12 +5127,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -5171,12 +5171,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -5193,12 +5193,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -5215,12 +5215,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5237,12 +5237,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Case Steps update core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -5259,12 +5259,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5325,12 +5325,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5347,12 +5347,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -5413,12 +5413,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -5435,12 +5435,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -5457,12 +5457,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -5479,12 +5479,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5567,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5589,12 +5589,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Arising Case from Original Case core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -5611,12 +5611,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
         </is>
       </c>
     </row>
@@ -5633,12 +5633,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
         </is>
       </c>
     </row>
@@ -5677,12 +5677,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
         </is>
       </c>
     </row>
@@ -5721,12 +5721,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -5765,12 +5765,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -5787,12 +5787,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -5875,12 +5875,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -5897,12 +5897,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -5919,12 +5919,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Bill Processing and Disbursement Module core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -5941,12 +5941,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6007,12 +6007,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -6117,12 +6117,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -6161,12 +6161,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Bi-directional CBS integration via secure REST API gateway for real-time account data and ledger sync.</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -6205,12 +6205,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -6249,12 +6249,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated dynamic PDF generation with official Bank Asia branding and digital/physical signature blocks.</t>
         </is>
       </c>
     </row>
@@ -6271,12 +6271,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -6403,12 +6403,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Court Fee Return and Adjustment core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -6447,12 +6447,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Transparent management and ledger tracking of unutilized court fees with return and future-case adjustment facilities.</t>
         </is>
       </c>
     </row>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Transparent management and ledger tracking of unutilized court fees with return and future-case adjustment facilities.</t>
         </is>
       </c>
     </row>
@@ -6491,12 +6491,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Transparent management and ledger tracking of unutilized court fees with return and future-case adjustment facilities.</t>
         </is>
       </c>
     </row>
@@ -6513,12 +6513,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Transparent management and ledger tracking of unutilized court fees with return and future-case adjustment facilities.</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -6579,12 +6579,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -6601,12 +6601,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Bi-directional CBS integration via secure REST API gateway for real-time account data and ledger sync.</t>
         </is>
       </c>
     </row>
@@ -6623,12 +6623,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -6711,12 +6711,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -6733,12 +6733,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -6777,12 +6777,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive HC &amp; AD Matters Feature core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated Supreme Court (High Court Division &amp; Appellate Division) suit management with case linking and order archiving.</t>
         </is>
       </c>
     </row>
@@ -6843,12 +6843,12 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -6865,12 +6865,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated Supreme Court (High Court Division &amp; Appellate Division) suit management with case linking and order archiving.</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated Supreme Court (High Court Division &amp; Appellate Division) suit management with case linking and order archiving.</t>
         </is>
       </c>
     </row>
@@ -6909,12 +6909,12 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated Supreme Court (High Court Division &amp; Appellate Division) suit management with case linking and order archiving.</t>
         </is>
       </c>
     </row>
@@ -6931,12 +6931,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -6953,12 +6953,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -7041,12 +7041,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -7063,12 +7063,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -7107,12 +7107,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -7129,12 +7129,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7151,12 +7151,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7173,12 +7173,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7195,12 +7195,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7239,12 +7239,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -7261,12 +7261,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -7283,12 +7283,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -7305,12 +7305,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7393,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7459,12 +7459,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7481,12 +7481,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7503,12 +7503,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7525,12 +7525,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7547,12 +7547,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -7591,12 +7591,12 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -7613,12 +7613,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -7657,12 +7657,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -7701,12 +7701,12 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -7723,12 +7723,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -7745,12 +7745,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Authorization Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
         </is>
       </c>
     </row>
@@ -7789,12 +7789,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
         </is>
       </c>
     </row>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
         </is>
       </c>
     </row>
@@ -7877,12 +7877,12 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -7943,12 +7943,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -7987,12 +7987,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated dynamic PDF generation with official Bank Asia branding and digital/physical signature blocks.</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -8031,12 +8031,12 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -8053,12 +8053,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -8075,12 +8075,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -8097,12 +8097,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Warrant Of Arrest Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end Warrant of Arrest (WOA) tracking, arrest history register, police station execution logs, and expense accounting.</t>
         </is>
       </c>
     </row>
@@ -8163,12 +8163,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end Warrant of Arrest (WOA) tracking, arrest history register, police station execution logs, and expense accounting.</t>
         </is>
       </c>
     </row>
@@ -8185,12 +8185,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8207,12 +8207,12 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -8229,12 +8229,12 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -8273,12 +8273,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -8361,12 +8361,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end Warrant of Arrest (WOA) tracking, arrest history register, police station execution logs, and expense accounting.</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Appeal Bail Money Deposit &amp; Withdraw Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Responsive web portal and secure mobile-optimized interface with MFA authentication for on-the-go legal officers.</t>
         </is>
       </c>
     </row>
@@ -8449,12 +8449,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8471,12 +8471,12 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8493,12 +8493,12 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Statutory appeal bail pre-deposit register, challan receipt archiving, withdrawal reconciliation, and audit trail.</t>
         </is>
       </c>
     </row>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -8537,12 +8537,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -8647,12 +8647,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -8669,12 +8669,12 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -8691,12 +8691,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -8713,12 +8713,12 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Responsive web portal and secure mobile-optimized interface with MFA authentication for on-the-go legal officers.</t>
         </is>
       </c>
     </row>
@@ -8735,12 +8735,12 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Responsive web portal and secure mobile-optimized interface with MFA authentication for on-the-go legal officers.</t>
         </is>
       </c>
     </row>
@@ -8757,12 +8757,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Statutory appeal bail pre-deposit register, challan receipt archiving, withdrawal reconciliation, and audit trail.</t>
         </is>
       </c>
     </row>
@@ -8779,12 +8779,12 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Statutory appeal bail pre-deposit register, challan receipt archiving, withdrawal reconciliation, and audit trail.</t>
         </is>
       </c>
     </row>
@@ -8801,12 +8801,12 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Document Upload core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8845,12 +8845,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8867,12 +8867,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8889,12 +8889,12 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8911,12 +8911,12 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -8977,12 +8977,12 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -9021,12 +9021,12 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Reports core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -9043,12 +9043,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Reporting সংযোজনী- ক- for BB) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Reporting সংযোজনী -খ for BB) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9087,12 +9087,12 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Reporting সংযোজনী-গ for BB) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9109,12 +9109,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Reporting. Total Case Summary/report for Management based on different nature of the case. with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9131,12 +9131,12 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Reporting/summery on cases by bank and against Bank in lower court/High Court. with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9153,12 +9153,12 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (RIT and BR-4 for BB) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9175,12 +9175,12 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (BB Audit-Artha Rin Suit) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9197,12 +9197,12 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for All Certificate Owned Property List [ (33(5) &amp; 33(7) separate certificate list] with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9219,12 +9219,12 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (DBI 22 to BB) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9241,12 +9241,12 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for District wise Artha Rin case Statement/Court Wise Statement and other parameter with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Major Financial Indicator with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9285,12 +9285,12 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for CRMR with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9307,12 +9307,12 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for ISS Report with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9329,12 +9329,12 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Statement of Classified Loans &amp; Advances and Other Information with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9351,12 +9351,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Statement of Pending Cases/disposed cases/settled cases on different parameter required bank with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Taskforce Report with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9395,12 +9395,12 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Bangladesh Bank Case related details Statement) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Portfolio summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Segment wise summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9461,12 +9461,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Officer wise summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Case Disposal Summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Step Completion Report with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9527,12 +9527,12 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Lawyer Wise Summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for LRM wise Case Statement Step changed with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9571,12 +9571,12 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Case Pending at The Same Steps with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9593,12 +9593,12 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Time Duration between Last date &amp; Next Date with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Summary on Lawyer's Performance with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Court Location Wise Summary with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9659,12 +9659,12 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for HCD &amp; AD Pending Cases Statement (Summary) with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9681,12 +9681,12 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for HCD &amp; AD Case Filed Statement with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9703,12 +9703,12 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for HCD &amp; AD Portfolio Summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9725,12 +9725,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Pending Cases Statement (Lawyer/Law Firm wise/branch wise/month wise/quarter wise/half yearly wise/yearly) with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9747,12 +9747,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Disposed Cases Statement (Lawyer/Law Firm wise/branch wise/month wise/quarter wise/half yearly wise/yearly) with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for 1st Legal Notice served Report with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9791,12 +9791,12 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for CMA Report with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Lawyer Wise Legal Notice with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9835,12 +9835,12 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Summery On Recovery on different parameter (monthly/quarterly/half yearly/yearly and other parameter as required. with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9857,12 +9857,12 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Summery On Next Steps with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Summery on Closed Accounts with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Account Wise Lawyer Bill with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9923,12 +9923,12 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Lawyer Bill Summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Court Fee Summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9967,12 +9967,12 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Account wise court fee with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Account wise publication bill with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -10011,12 +10011,12 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Report/summery on Auction (u/s-12/33(1),33(4), 33(5), of Artharin Adalat Ain) published (monthly wise/Quarterly/half yearly/yearly) with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Report/summary on summons notice published in Newspaper (monthly wise/Quarterly/half yearly/yearly) with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -10055,12 +10055,12 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Ensuring reporting as BB Risk Base Audit module newly introduced by BB) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Report/summery on legal expenses incurred already or to be incurred on different parameters (monthly wise/Quarterly/half yearly/yearly) with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -10099,12 +10099,12 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Notification core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -10121,12 +10121,12 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated notification dispatcher for 60-day decree execution, 2-3 day hearing reminders, dormant cases, and lawyer updates.</t>
         </is>
       </c>
     </row>
@@ -10143,12 +10143,12 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated notification dispatcher for 60-day decree execution, 2-3 day hearing reminders, dormant cases, and lawyer updates.</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -10209,12 +10209,12 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -10231,12 +10231,12 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -10253,12 +10253,12 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated notification dispatcher for 60-day decree execution, 2-3 day hearing reminders, dormant cases, and lawyer updates.</t>
         </is>
       </c>
     </row>
@@ -10275,12 +10275,12 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Customer 360 Search core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -10297,12 +10297,12 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Unified Customer 360 view aggregating all litigation cases, CBS accounts, security collateral, WOA, and communication history.</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Unified Customer 360 view aggregating all litigation cases, CBS accounts, security collateral, WOA, and communication history.</t>
         </is>
       </c>
     </row>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -10363,12 +10363,12 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Legal Memos and Notices Publication core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -10385,12 +10385,12 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10407,12 +10407,12 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10429,12 +10429,12 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10451,12 +10451,12 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10473,12 +10473,12 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive System Settings core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -10495,12 +10495,12 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10517,12 +10517,12 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10539,12 +10539,12 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10561,12 +10561,12 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10583,12 +10583,12 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10605,12 +10605,12 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10627,12 +10627,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10671,12 +10671,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10693,12 +10693,12 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10715,12 +10715,12 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10737,12 +10737,12 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10803,12 +10803,12 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10825,12 +10825,12 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Legal Opinion Management System core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -10847,12 +10847,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal opinion vetting repository and task delegation module with TAT tracking and deadline alerts.</t>
         </is>
       </c>
     </row>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal opinion vetting repository and task delegation module with TAT tracking and deadline alerts.</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Task Management System core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -10913,12 +10913,12 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal opinion vetting repository and task delegation module with TAT tracking and deadline alerts.</t>
         </is>
       </c>
     </row>
@@ -10935,12 +10935,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal opinion vetting repository and task delegation module with TAT tracking and deadline alerts.</t>
         </is>
       </c>
     </row>
